--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="34">
   <si>
     <t xml:space="preserve">캐릭터 고유 ID</t>
   </si>
@@ -61,9 +61,6 @@
     <t xml:space="preserve">IconPath</t>
   </si>
   <si>
-    <t xml:space="preserve">Item_Gold_0001</t>
-  </si>
-  <si>
     <t xml:space="preserve">화폐</t>
   </si>
   <si>
@@ -79,9 +76,6 @@
     <t xml:space="preserve">Icon/Icon_Item_Gold_0001</t>
   </si>
   <si>
-    <t xml:space="preserve">Item_Fuel_0002</t>
-  </si>
-  <si>
     <t xml:space="preserve">연료</t>
   </si>
   <si>
@@ -92,9 +86,6 @@
   </si>
   <si>
     <t xml:space="preserve">Icon/Icon_Item_Fuel_0002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item_Supplies_0003</t>
   </si>
   <si>
     <t xml:space="preserve">보급품</t>
@@ -125,9 +116,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Item_TradingGoods_0004</t>
-  </si>
-  <si>
     <t xml:space="preserve">교역품 1</t>
   </si>
   <si>
@@ -156,25 +144,16 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Item_TradingGoods_0005</t>
-  </si>
-  <si>
     <t xml:space="preserve">교역품 2</t>
   </si>
   <si>
     <t xml:space="preserve">Icon/Icon_Item_TradingGoods_0005</t>
   </si>
   <si>
-    <t xml:space="preserve">Item_TradingGoods_0006</t>
-  </si>
-  <si>
     <t xml:space="preserve">교역품 3</t>
   </si>
   <si>
     <t xml:space="preserve">Icon/Icon_Item_TradingGoods_0006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item_TradingGoods_0007</t>
   </si>
   <si>
     <t xml:space="preserve">교역품 4</t>
@@ -676,20 +655,20 @@
       <c r="N3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="2" t="n">
+        <v>1001001</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>16</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>17</v>
       </c>
       <c r="F4" s="8" t="n">
         <v>1</v>
@@ -698,7 +677,7 @@
         <v>999999999</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
@@ -707,20 +686,20 @@
       <c r="M4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="2" t="n">
+        <v>1001002</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="D5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>20</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>22</v>
       </c>
       <c r="F5" s="8" t="n">
         <v>10</v>
@@ -729,7 +708,7 @@
         <v>1000</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
@@ -738,20 +717,20 @@
       <c r="M5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>24</v>
+      <c r="A6" s="2" t="n">
+        <v>1001003</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>20</v>
@@ -760,7 +739,7 @@
         <v>1000</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I6" s="8"/>
       <c r="K6" s="8"/>
@@ -768,20 +747,20 @@
       <c r="M6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>28</v>
+      <c r="A7" s="2" t="n">
+        <v>1001004</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F7" s="8" t="n">
         <v>10</v>
@@ -790,7 +769,7 @@
         <v>10</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
@@ -799,20 +778,20 @@
       <c r="M7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>32</v>
+      <c r="A8" s="2" t="n">
+        <v>1001005</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>30</v>
@@ -821,7 +800,7 @@
         <v>10</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -830,20 +809,20 @@
       <c r="M8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>35</v>
+      <c r="A9" s="2" t="n">
+        <v>1001006</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F9" s="8" t="n">
         <v>50</v>
@@ -852,7 +831,7 @@
         <v>10</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
@@ -861,20 +840,20 @@
       <c r="M9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>38</v>
+      <c r="A10" s="2" t="n">
+        <v>1001007</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>100</v>
@@ -883,7 +862,7 @@
         <v>10</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
   <si>
     <t xml:space="preserve">캐릭터 고유 ID</t>
   </si>
@@ -61,6 +61,9 @@
     <t xml:space="preserve">IconPath</t>
   </si>
   <si>
+    <t xml:space="preserve">Gold_0001</t>
+  </si>
+  <si>
     <t xml:space="preserve">화폐</t>
   </si>
   <si>
@@ -76,6 +79,9 @@
     <t xml:space="preserve">Icon/Icon_Item_Gold_0001</t>
   </si>
   <si>
+    <t xml:space="preserve">Fuel_0002</t>
+  </si>
+  <si>
     <t xml:space="preserve">연료</t>
   </si>
   <si>
@@ -86,6 +92,9 @@
   </si>
   <si>
     <t xml:space="preserve">Icon/Icon_Item_Fuel_0002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplies_0003</t>
   </si>
   <si>
     <t xml:space="preserve">보급품</t>
@@ -116,6 +125,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">TradingGoods_0004</t>
+  </si>
+  <si>
     <t xml:space="preserve">교역품 1</t>
   </si>
   <si>
@@ -144,16 +156,25 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">TradingGoods_0005</t>
+  </si>
+  <si>
     <t xml:space="preserve">교역품 2</t>
   </si>
   <si>
     <t xml:space="preserve">Icon/Icon_Item_TradingGoods_0005</t>
   </si>
   <si>
+    <t xml:space="preserve">TradingGoods_0006</t>
+  </si>
+  <si>
     <t xml:space="preserve">교역품 3</t>
   </si>
   <si>
     <t xml:space="preserve">Icon/Icon_Item_TradingGoods_0006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TradingGoods_0007</t>
   </si>
   <si>
     <t xml:space="preserve">교역품 4</t>
@@ -292,7 +313,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -327,6 +348,10 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -655,20 +680,20 @@
       <c r="N3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
-        <v>1001001</v>
+      <c r="A4" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" s="8" t="n">
         <v>1</v>
@@ -677,7 +702,7 @@
         <v>999999999</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
@@ -686,20 +711,20 @@
       <c r="M4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
-        <v>1001002</v>
+      <c r="A5" s="9" t="s">
+        <v>19</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F5" s="8" t="n">
         <v>10</v>
@@ -708,7 +733,7 @@
         <v>1000</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
@@ -717,20 +742,20 @@
       <c r="M5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
-        <v>1001003</v>
+      <c r="A6" s="9" t="s">
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>22</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>20</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>20</v>
@@ -739,7 +764,7 @@
         <v>1000</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I6" s="8"/>
       <c r="K6" s="8"/>
@@ -747,20 +772,20 @@
       <c r="M6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
-        <v>1001004</v>
+      <c r="A7" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F7" s="8" t="n">
         <v>10</v>
@@ -769,7 +794,7 @@
         <v>10</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
@@ -778,20 +803,20 @@
       <c r="M7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
-        <v>1001005</v>
+      <c r="A8" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>30</v>
@@ -800,7 +825,7 @@
         <v>10</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -809,20 +834,20 @@
       <c r="M8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
-        <v>1001006</v>
+      <c r="A9" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>26</v>
-      </c>
       <c r="E9" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F9" s="8" t="n">
         <v>50</v>
@@ -831,7 +856,7 @@
         <v>10</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
@@ -840,20 +865,20 @@
       <c r="M9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
-        <v>1001007</v>
+      <c r="A10" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>100</v>
@@ -862,7 +887,7 @@
         <v>10</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
   <si>
     <t xml:space="preserve">캐릭터 고유 ID</t>
   </si>
@@ -49,7 +49,7 @@
     <t xml:space="preserve">ItemType</t>
   </si>
   <si>
-    <t xml:space="preserve">Grade</t>
+    <t xml:space="preserve">Category</t>
   </si>
   <si>
     <t xml:space="preserve">Price</t>
@@ -73,7 +73,7 @@
     <t xml:space="preserve">valuable</t>
   </si>
   <si>
-    <t xml:space="preserve">Legend</t>
+    <t xml:space="preserve">Coin</t>
   </si>
   <si>
     <t xml:space="preserve">Icon/Icon_Item_Gold_0001</t>
@@ -88,7 +88,7 @@
     <t xml:space="preserve">연료다. 보통은 석탄이다</t>
   </si>
   <si>
-    <t xml:space="preserve">Normal</t>
+    <t xml:space="preserve">Raw</t>
   </si>
   <si>
     <t xml:space="preserve">Icon/Icon_Item_Fuel_0002</t>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t xml:space="preserve">식량, 자재, 탄약 등</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumables</t>
   </si>
   <si>
     <r>
@@ -162,6 +165,9 @@
     <t xml:space="preserve">교역품 2</t>
   </si>
   <si>
+    <t xml:space="preserve">Processed</t>
+  </si>
+  <si>
     <t xml:space="preserve">Icon/Icon_Item_TradingGoods_0005</t>
   </si>
   <si>
@@ -171,6 +177,9 @@
     <t xml:space="preserve">교역품 3</t>
   </si>
   <si>
+    <t xml:space="preserve">Finished</t>
+  </si>
+  <si>
     <t xml:space="preserve">Icon/Icon_Item_TradingGoods_0006</t>
   </si>
   <si>
@@ -178,6 +187,9 @@
   </si>
   <si>
     <t xml:space="preserve">교역품 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luxury</t>
   </si>
   <si>
     <t xml:space="preserve">Icon/Icon_Item_TradingGoods_0007</t>
@@ -190,7 +202,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -243,6 +255,13 @@
       <name val="DotumChe"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
@@ -313,7 +332,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -352,6 +371,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -605,16 +628,18 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N1000"/>
-  <sheetFormatPr defaultColWidth="11.53125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="46.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.37"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="30.79"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="9" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="15" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="5.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="28.05"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="9" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="15" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -754,8 +779,8 @@
       <c r="D6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>22</v>
+      <c r="E6" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>20</v>
@@ -764,7 +789,7 @@
         <v>1000</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I6" s="8"/>
       <c r="K6" s="8"/>
@@ -773,16 +798,16 @@
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>22</v>
@@ -791,10 +816,10 @@
         <v>10</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
@@ -804,28 +829,28 @@
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>22</v>
+        <v>31</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>30</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
@@ -835,28 +860,28 @@
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>22</v>
+        <v>31</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="F9" s="8" t="n">
         <v>50</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
@@ -866,28 +891,28 @@
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>22</v>
+        <v>31</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>100</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
@@ -956,12 +981,12 @@
       <c r="M14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
